--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/Tapi.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/Tapi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712E8F37-39BF-412B-9E3F-BFF6124941AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A51F216-A11D-4521-8C03-BA765F11B372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -420,25 +420,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -458,6 +443,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -740,128 +740,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-    </row>
-    <row r="2" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-    </row>
-    <row r="3" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-    </row>
-    <row r="4" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="18">
         <v>8</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18">
         <v>8</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18">
         <v>10</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13">
+      <c r="I4" s="18"/>
+      <c r="J4" s="18">
         <v>4</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13">
+      <c r="K4" s="18"/>
+      <c r="L4" s="18">
         <v>4</v>
       </c>
-      <c r="M4" s="13"/>
+      <c r="M4" s="18"/>
       <c r="N4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="15" t="s">
+    <row r="5" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15" t="s">
+      <c r="G5" s="22"/>
+      <c r="H5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="22"/>
+      <c r="J5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="22"/>
+      <c r="L5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="15"/>
+      <c r="M5" s="22"/>
       <c r="N5" s="2">
         <f>D4+F4+H4+J4+L4</f>
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="32.6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -903,7 +903,7 @@
       </c>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -933,7 +933,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -963,7 +963,7 @@
       </c>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -989,7 +989,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1041,7 +1041,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1097,7 +1097,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>31</v>
       </c>
@@ -1127,7 +1127,7 @@
       <c r="M14" s="6"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>33</v>
       </c>
@@ -1161,7 +1161,7 @@
       <c r="M15" s="5"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
@@ -1187,7 +1187,7 @@
       <c r="M16" s="6"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
@@ -1213,7 +1213,7 @@
       <c r="M17" s="6"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1229,12 +1229,12 @@
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
     </row>
-    <row r="19" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+    <row r="19" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="1">
         <f>SUM(D14:D18)</f>
         <v>6</v>
@@ -1264,25 +1264,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-    </row>
-    <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>31</v>
       </c>
@@ -1308,7 +1308,7 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
     </row>
-    <row r="22" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>40</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
     </row>
-    <row r="23" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>40</v>
       </c>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N23" s="4"/>
     </row>
-    <row r="24" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>40</v>
       </c>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="N24" s="4"/>
     </row>
-    <row r="25" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>44</v>
       </c>
@@ -1412,7 +1412,7 @@
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
     </row>
-    <row r="26" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>33</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
     </row>
-    <row r="27" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>35</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
     </row>
-    <row r="28" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>35</v>
       </c>
@@ -1490,7 +1490,7 @@
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
     </row>
-    <row r="29" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>35</v>
       </c>
@@ -1516,7 +1516,7 @@
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
     </row>
-    <row r="30" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>35</v>
       </c>
@@ -1542,12 +1542,12 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
     </row>
-    <row r="31" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+    <row r="31" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
       <c r="D31" s="1">
         <f>SUM(D21:D30)</f>
         <v>2</v>
@@ -1577,12 +1577,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+    <row r="32" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
       <c r="D32" s="1">
         <f>+D19+D31</f>
         <v>8</v>
@@ -1615,6 +1615,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -1625,15 +1634,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1642,128 +1642,128 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-    </row>
-    <row r="2" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-    </row>
-    <row r="3" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-    </row>
-    <row r="4" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+    </row>
+    <row r="3" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="18">
         <v>4</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18">
         <v>4</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18">
         <v>4</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13">
+      <c r="I4" s="18"/>
+      <c r="J4" s="18">
         <v>0</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13">
+      <c r="K4" s="18"/>
+      <c r="L4" s="18">
         <v>0</v>
       </c>
-      <c r="M4" s="13"/>
+      <c r="M4" s="18"/>
       <c r="N4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="15" t="s">
+    <row r="5" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15" t="s">
+      <c r="G5" s="22"/>
+      <c r="H5" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="22"/>
+      <c r="J5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="22"/>
+      <c r="L5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="15"/>
+      <c r="M5" s="22"/>
       <c r="N5" s="2">
         <f>D4+F4+H4+J4+L4</f>
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="32.6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1835,7 +1835,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1943,7 +1943,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1999,7 +1999,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>33</v>
       </c>
@@ -2025,7 +2025,7 @@
       <c r="M14" s="6"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>33</v>
       </c>
@@ -2051,7 +2051,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -2067,7 +2067,7 @@
       <c r="M16" s="6"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2083,12 +2083,12 @@
       <c r="M17" s="6"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="1">
         <f>SUM(D14:D15)</f>
         <v>0</v>
@@ -2118,25 +2118,25 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-    </row>
-    <row r="20" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -2162,7 +2162,7 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
     </row>
-    <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>31</v>
       </c>
@@ -2188,7 +2188,7 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
     </row>
-    <row r="22" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>35</v>
       </c>
@@ -2214,7 +2214,7 @@
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
     </row>
-    <row r="23" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
@@ -2240,7 +2240,7 @@
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
     </row>
-    <row r="24" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
@@ -2256,12 +2256,12 @@
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
     </row>
-    <row r="25" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+    <row r="25" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="1">
         <f>SUM(D20:D23)</f>
         <v>4</v>
@@ -2291,12 +2291,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+    <row r="26" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
       <c r="D26" s="1">
         <f>+D18+D25</f>
         <v>4</v>
@@ -2329,6 +2329,15 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A19:N19"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -2339,15 +2348,6 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="A19:N19"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
